--- a/Result/profitability/3580.xlsx
+++ b/Result/profitability/3580.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.92</v>
+        <v>0.6675</v>
       </c>
       <c r="N2" t="n">
-        <v>46.22375</v>
+        <v>47.34875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.86</v>
       </c>
       <c r="M3" t="n">
-        <v>0.79625</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>42.215</v>
+        <v>44.02</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.51</v>
       </c>
       <c r="M4" t="n">
-        <v>0.78</v>
+        <v>0.8387500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>44.1125</v>
+        <v>46.36375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7237500000000001</v>
+        <v>0.75125</v>
       </c>
       <c r="N5" t="n">
-        <v>41.5825</v>
+        <v>41.19125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>0.73875</v>
+        <v>0.7812500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>36.55375</v>
+        <v>36.69625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6625000000000001</v>
+        <v>0.70625</v>
       </c>
       <c r="N7" t="n">
-        <v>33.23625</v>
+        <v>32.1425</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6362500000000001</v>
+        <v>0.7625</v>
       </c>
       <c r="N8" t="n">
-        <v>28.63625</v>
+        <v>31.14625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="N9" t="n">
         <v>27.6725</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3580</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>125</v>
+      </c>
+      <c r="D74" t="n">
+        <v>56</v>
+      </c>
+      <c r="E74" t="n">
+        <v>69</v>
+      </c>
+      <c r="F74" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="G74" t="n">
+        <v>42</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>33.40%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>43</v>
+      </c>
+      <c r="K74" t="n">
+        <v>33</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N74" t="n">
+        <v>48.72125</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-5.611111111111111</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.5738782509288367</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.360655737704918</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>-3.130000000000003</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>-0.05378006872852237</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
